--- a/Data Files/Backoffce/GeraBlocoBCadastroCorretorData/GeraBlocoBCadastroCorretor - Copia.xlsx
+++ b/Data Files/Backoffce/GeraBlocoBCadastroCorretorData/GeraBlocoBCadastroCorretor - Copia.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20373"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\GeraBlocoBCadastroCorretorData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A48B52-214F-4175-ADAC-19821CB59796}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F50F24-1C55-4702-A202-22F40AA4CAFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="GeraBlocoBCadastroCorretor" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">GeraBlocoBCadastroCorretor!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">GeraBlocoBCadastroCorretor!$A$1:$C$1</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="5">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -36,13 +36,13 @@
     <t>Mensagem</t>
   </si>
   <si>
-    <t>Processar</t>
-  </si>
-  <si>
     <t>Codigo</t>
   </si>
   <si>
-    <t>Erro</t>
+    <t>Processado</t>
+  </si>
+  <si>
+    <t>Ramos ativados</t>
   </si>
 </sst>
 </file>
@@ -93,7 +93,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -110,30 +110,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -446,66 +453,367 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="16.42578125" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="74.85546875" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" style="3" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="16.42578125" style="3" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="74.85546875" style="3" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.140625" style="3" collapsed="1"/>
+    <col min="5" max="5" width="9.140625" style="3"/>
+    <col min="6" max="16384" width="9.140625" style="3" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
-        <v>4020393</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-    </row>
-    <row r="3" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
-        <v>4020394</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>4020395</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>4035232</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>4035235</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>4035228</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>4035241</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>4035226</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>4035222</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>4035227</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>4035218</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>4035237</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>4035238</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>4035239</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>4035215</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>4035240</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>4035234</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>4035224</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>4035242</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>4035214</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>4035216</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>4035233</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>4035221</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>4035231</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>4035220</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>4035230</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>4035219</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
+        <v>4035229</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="8"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
+        <v>4035244</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" s="8"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
+        <v>4035245</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" s="8"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
+        <v>4035217</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" s="8"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
+        <v>4035225</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" s="8"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
+        <v>4035223</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" s="8"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
+        <v>4035243</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32" s="8"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
+        <v>4035236</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:C1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A2:A4">
-    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -517,31 +825,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>